--- a/public/templates/請求書現金.xlsx
+++ b/public/templates/請求書現金.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26bd8b67dbe05400/ドキュメント/ケアサービス　たんでん/顧客情報請求あり/3 石川　啓(集金)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26bd8b67dbe05400/ドキュメント/ケアサービス　たんでん/各種資料　原本/請求書/アプリ用テンプレ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="8_{3DB82A3E-4CBD-47EB-9DB0-79D45A52FD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C75716BD-E64E-4E3A-9FF7-62BAB0FAC93E}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="8_{3DB82A3E-4CBD-47EB-9DB0-79D45A52FD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6386A7F2-5966-4B84-A32C-6E885A3FC7AA}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5209DA7A-5152-4F99-B3B1-55AC7DC7D125}"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <r>
       <t>請求書</t>
@@ -325,22 +325,6 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>任意代理人　月額管理 金銭管理　郵便管理</t>
-    <rPh sb="11" eb="13">
-      <t>キンセン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ユウビン</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>有料道路　470円</t>
     <rPh sb="0" eb="4">
       <t>ユウリョウドウロ</t>
@@ -404,27 +388,6 @@
   </si>
   <si>
     <t>集金</t>
-  </si>
-  <si>
-    <t>〒751-0826 下関市後田町4-13-5</t>
-    <rPh sb="10" eb="13">
-      <t>シモノセキシ</t>
-    </rPh>
-    <rPh sb="13" eb="16">
-      <t>ウシロダチョウ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>石川　啓</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>ごみ捨て</t>
-    <rPh sb="2" eb="3">
-      <t>ス</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -1225,1078 +1188,7 @@
     <cellStyle name="標準 9" xfId="1" xr:uid="{CBF6CAA7-4E5D-41DF-B58C-1C02695E7ACA}"/>
     <cellStyle name="表の詳細 (右揃え)" xfId="5" xr:uid="{8F5B24CB-63DD-4893-BA63-312EEACBEF38}"/>
   </cellStyles>
-  <dxfs count="102">
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="1" tint="0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2416,6 +1308,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2763,9 +1659,7 @@
       <c r="F2" s="37"/>
       <c r="G2" s="38"/>
       <c r="H2" s="39"/>
-      <c r="I2" s="19" t="s">
-        <v>39</v>
-      </c>
+      <c r="I2" s="19"/>
       <c r="J2" s="41"/>
       <c r="K2" s="41"/>
       <c r="L2" s="41"/>
@@ -2776,7 +1670,7 @@
     </row>
     <row r="3" spans="1:20" ht="21.75" customHeight="1">
       <c r="A3" s="42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="43"/>
       <c r="C3" s="43"/>
@@ -2796,7 +1690,7 @@
     </row>
     <row r="4" spans="1:20" ht="14.25" customHeight="1">
       <c r="A4" s="42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" s="43"/>
       <c r="C4" s="43"/>
@@ -2816,7 +1710,7 @@
     </row>
     <row r="5" spans="1:20" ht="41.25" customHeight="1">
       <c r="A5" s="46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="47"/>
       <c r="C5" s="47"/>
@@ -2825,18 +1719,16 @@
       <c r="F5" s="47"/>
       <c r="G5" s="47"/>
       <c r="H5" s="45"/>
-      <c r="I5" s="32" t="s">
-        <v>40</v>
-      </c>
+      <c r="I5" s="32"/>
       <c r="J5" s="48"/>
       <c r="K5" s="48"/>
       <c r="L5" s="48"/>
       <c r="M5" s="49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N5" s="49">
         <f>I13</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O5" s="50" t="s">
         <v>1</v>
@@ -2937,7 +1829,7 @@
     <row r="11" spans="1:20" s="2" customFormat="1" ht="27" customHeight="1">
       <c r="A11" s="66">
         <f>O29</f>
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="B11" s="67"/>
       <c r="C11" s="67"/>
@@ -2946,9 +1838,9 @@
       <c r="F11" s="68"/>
       <c r="G11" s="54"/>
       <c r="H11" s="54"/>
-      <c r="I11" s="117" t="str">
+      <c r="I11" s="117">
         <f>I5</f>
-        <v>石川　啓</v>
+        <v>0</v>
       </c>
       <c r="J11" s="69"/>
       <c r="K11" s="69"/>
@@ -2992,9 +1884,7 @@
       <c r="H13" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="I13" s="3">
-        <v>7</v>
-      </c>
+      <c r="I13" s="3"/>
       <c r="J13" s="76" t="s">
         <v>8</v>
       </c>
@@ -3043,9 +1933,7 @@
       <c r="A15" s="15"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
-      <c r="D15" s="27" t="s">
-        <v>41</v>
-      </c>
+      <c r="D15" s="27"/>
       <c r="E15" s="81"/>
       <c r="F15" s="81"/>
       <c r="G15" s="81"/>
@@ -3056,9 +1944,7 @@
       <c r="L15" s="23"/>
       <c r="M15" s="17"/>
       <c r="N15" s="31"/>
-      <c r="O15" s="21">
-        <v>500</v>
-      </c>
+      <c r="O15" s="21"/>
     </row>
     <row r="16" spans="1:20" ht="21" customHeight="1">
       <c r="A16" s="15"/>
@@ -3218,7 +2104,7 @@
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E25" s="81"/>
       <c r="F25" s="81"/>
@@ -3239,9 +2125,7 @@
       <c r="A26" s="22"/>
       <c r="B26" s="26"/>
       <c r="C26" s="26"/>
-      <c r="D26" s="27" t="s">
-        <v>27</v>
-      </c>
+      <c r="D26" s="27"/>
       <c r="E26" s="81"/>
       <c r="F26" s="81"/>
       <c r="G26" s="81"/>
@@ -3273,7 +2157,7 @@
       <c r="N27" s="89"/>
       <c r="O27" s="83">
         <f>O29-O28</f>
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="21" customHeight="1">
@@ -3317,7 +2201,7 @@
       <c r="N29" s="94"/>
       <c r="O29" s="95">
         <f>SUM(O15:O26)</f>
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="18.75" customHeight="1">
@@ -3415,7 +2299,7 @@
         <v>23</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D35" s="102" t="s">
         <v>24</v>
@@ -3425,7 +2309,7 @@
       <c r="G35" s="104"/>
       <c r="H35" s="104"/>
       <c r="I35" s="119" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J35" s="119"/>
       <c r="K35" s="119"/>
@@ -3472,7 +2356,7 @@
     <row r="38" spans="1:33" ht="27" customHeight="1">
       <c r="A38" s="66">
         <f>A11</f>
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="B38" s="67"/>
       <c r="C38" s="67"/>
@@ -3537,24 +2421,24 @@
         <v>26</v>
       </c>
       <c r="B40" s="111" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C40" s="112">
         <f>G13</f>
         <v>8</v>
       </c>
       <c r="D40" s="113" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E40" s="113">
         <f>I13</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F40" s="114" t="s">
+        <v>34</v>
+      </c>
+      <c r="G40" s="115" t="s">
         <v>35</v>
-      </c>
-      <c r="G40" s="115" t="s">
-        <v>36</v>
       </c>
       <c r="H40" s="116"/>
       <c r="I40" s="119"/>
